--- a/data/team_stats/2025-26NBA_RegularSeason_Team_stats.xlsx
+++ b/data/team_stats/2025-26NBA_RegularSeason_Team_stats.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,1152 +429,1152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>entityid</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>teamid</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>shortname</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>rowid</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>teamabbreviation</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>secondsplayed</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>gamesplayed</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>plusminus</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>offposs</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>defposs</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>penaltyoffposs</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>penaltydefposs</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>secondchanceoffposs</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>totalposs</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>atrimfgm</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>atrimfga</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>secondchanceatrimfgm</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>secondchanceatrimfga</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>penaltyatrimfgm</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>penaltyatrimfga</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>shortmidrangefgm</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>shortmidrangefga</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>longmidrangefgm</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>longmidrangefga</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>corner3fgm</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>corner3fga</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>secondchancecorner3fgm</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>secondchancecorner3fga</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>penaltycorner3fgm</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>penaltycorner3fga</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>arc3fgm</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>arc3fga</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>secondchancearc3fgm</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>secondchancearc3fga</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>penaltyarc3fgm</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>penaltyarc3fga</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>fg2m</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>fg2a</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>fg3m</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>fg3a</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>ftpoints</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>opponentpoints</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>secondchancefg2m</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>secondchancefg2a</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>secondchancefg3m</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>secondchancefg3a</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>secondchanceftpoints</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>secondchancepoints</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>penaltyfg2m</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>penaltyfg2a</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>penaltyfg3m</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>penaltyfg3a</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>penaltyftpoints</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>penaltypoints</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>ptsassisted2s</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>ptsunassisted2s</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>ptsassisted3s</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>ptsunassisted3s</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>ptsputbacks</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>nonheavearc3fga</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>nonheavearc3fgm</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>fg2ablocked</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>fg3ablocked</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>twoptassists</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>threeptassists</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>assists</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>arc3assists</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>corner3assists</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>atrimassists</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>shortmidrangeassists</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>longmidrangeassists</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>assistpoints</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>offthreeptrebounds</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>offtwoptrebounds</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>ftoffrebounds</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>defthreeptrebounds</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>deftwoptrebounds</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>ftdefrebounds</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>defrebounds</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>offrebounds</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>rebounds</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>selforeb</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>steals</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>badpasssteals</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>lostballsteals</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>liveballturnovers</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>badpassoutofboundsturnovers</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>badpassturnovers</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>deadballturnovers</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>lostballoutofboundsturnovers</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>lostballturnovers</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>stepoutofboundsturnovers</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>travels</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>turnovers</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>secondchanceturnovers</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>penaltyturnovers</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>shootingfouls</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>fouls</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>charge fouls</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>clear path fouls</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>loose ball fouls</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>offensive fouls</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>foulsdrawn</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>charge fouls drawn</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>loose ball fouls drawn</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>offensive fouls drawn</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>fta</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>2pt and 1 free throw trips</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>3pt and 1 free throw trips</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>technical free throw trips</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>twoptshootingfoulsdrawn</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>threeptshootingfoulsdrawn</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>nonshootingfoulsdrawn</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>blocked2s</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>blocked3s</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>blockedarc3</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>blockedatrim</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>blockedcorner3</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>blockedlongmidrange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>blockedshortmidrange</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>blocks</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>recoveredblocks</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>defensivegoaltends</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>offensivegoaltends</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>defensive 3 seconds violations</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>firstchancepoints</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>penaltypointsexcludingtakefouls</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>penaltyoffpossexcludingtakefouls</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>nonshootingpenaltynontakefouls</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>nonshootingpenaltynontakefoulsdrawn</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>assisted2spct</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>nonputbacksassisted2spct</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>assisted3spct</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>fg3pct</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>secondchancefg3pct</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>penaltyfg3pct</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>nonheavefg3pct</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>fg2pct</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>secondchancefg2pct</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>penaltyfg2pct</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>efgpct</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>secondchanceefgpct</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>penaltyefgpct</t>
         </is>
       </c>
-      <c r="EP1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>tspct</t>
         </is>
       </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>secondchancetspct</t>
         </is>
       </c>
-      <c r="ER1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>penaltytspct</t>
         </is>
       </c>
-      <c r="ES1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>fg3apct</t>
         </is>
       </c>
-      <c r="ET1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>fg3apctblocked</t>
         </is>
       </c>
-      <c r="EU1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>fg2apctblocked</t>
         </is>
       </c>
-      <c r="EV1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>atrimpctblocked</t>
         </is>
       </c>
-      <c r="EW1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>shortmidrangepctblocked</t>
         </is>
       </c>
-      <c r="EX1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>longmidrangepctblocked</t>
         </is>
       </c>
-      <c r="EY1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>corner3pctblocked</t>
         </is>
       </c>
-      <c r="EZ1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>arc3pctblocked</t>
         </is>
       </c>
-      <c r="FA1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>liveballturnoverpct</t>
         </is>
       </c>
-      <c r="FB1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>defftreboundpct</t>
         </is>
       </c>
-      <c r="FC1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>offftreboundpct</t>
         </is>
       </c>
-      <c r="FD1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>deftwoptreboundpct</t>
         </is>
       </c>
-      <c r="FE1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>offtwoptreboundpct</t>
         </is>
       </c>
-      <c r="FF1" t="inlineStr">
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>defthreeptreboundpct</t>
         </is>
       </c>
-      <c r="FG1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>offthreeptreboundpct</t>
         </is>
       </c>
-      <c r="FH1" t="inlineStr">
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>deffgreboundpct</t>
         </is>
       </c>
-      <c r="FI1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>offfgreboundpct</t>
         </is>
       </c>
-      <c r="FJ1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>offatrimreboundpct</t>
         </is>
       </c>
-      <c r="FK1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>offshortmidrangereboundpct</t>
         </is>
       </c>
-      <c r="FL1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>offlongmidrangereboundpct</t>
         </is>
       </c>
-      <c r="FM1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>offarc3reboundpct</t>
         </is>
       </c>
-      <c r="FN1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>offcorner3reboundpct</t>
         </is>
       </c>
-      <c r="FO1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>defatrimreboundpct</t>
         </is>
       </c>
-      <c r="FP1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>defshortmidrangereboundpct</t>
         </is>
       </c>
-      <c r="FQ1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>deflongmidrangereboundpct</t>
         </is>
       </c>
-      <c r="FR1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>defarc3reboundpct</t>
         </is>
       </c>
-      <c r="FS1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>defcorner3reboundpct</t>
         </is>
       </c>
-      <c r="FT1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>selforebpct</t>
         </is>
       </c>
-      <c r="FU1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>pace</t>
         </is>
       </c>
-      <c r="FV1" t="inlineStr">
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>blocksrecoveredpct</t>
         </is>
       </c>
-      <c r="FW1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
         <is>
           <t>secondsperpossoff</t>
         </is>
       </c>
-      <c r="FX1" t="inlineStr">
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>secondsperpossdef</t>
         </is>
       </c>
-      <c r="FY1" t="inlineStr">
+      <c r="FY1" s="1" t="inlineStr">
         <is>
           <t>secondsexcludingorebsperpossoff</t>
         </is>
       </c>
-      <c r="FZ1" t="inlineStr">
+      <c r="FZ1" s="1" t="inlineStr">
         <is>
           <t>secondsexcludingorebsperpossdef</t>
         </is>
       </c>
-      <c r="GA1" t="inlineStr">
+      <c r="GA1" s="1" t="inlineStr">
         <is>
           <t>atrimfrequency</t>
         </is>
       </c>
-      <c r="GB1" t="inlineStr">
+      <c r="GB1" s="1" t="inlineStr">
         <is>
           <t>atrimaccuracy</t>
         </is>
       </c>
-      <c r="GC1" t="inlineStr">
+      <c r="GC1" s="1" t="inlineStr">
         <is>
           <t>unblockedatrimaccuracy</t>
         </is>
       </c>
-      <c r="GD1" t="inlineStr">
+      <c r="GD1" s="1" t="inlineStr">
         <is>
           <t>atrimpctassisted</t>
         </is>
       </c>
-      <c r="GE1" t="inlineStr">
+      <c r="GE1" s="1" t="inlineStr">
         <is>
           <t>shortmidrangefrequency</t>
         </is>
       </c>
-      <c r="GF1" t="inlineStr">
+      <c r="GF1" s="1" t="inlineStr">
         <is>
           <t>shortmidrangeaccuracy</t>
         </is>
       </c>
-      <c r="GG1" t="inlineStr">
+      <c r="GG1" s="1" t="inlineStr">
         <is>
           <t>unblockedshortmidrangeaccuracy</t>
         </is>
       </c>
-      <c r="GH1" t="inlineStr">
+      <c r="GH1" s="1" t="inlineStr">
         <is>
           <t>shortmidrangepctassisted</t>
         </is>
       </c>
-      <c r="GI1" t="inlineStr">
+      <c r="GI1" s="1" t="inlineStr">
         <is>
           <t>longmidrangefrequency</t>
         </is>
       </c>
-      <c r="GJ1" t="inlineStr">
+      <c r="GJ1" s="1" t="inlineStr">
         <is>
           <t>longmidrangeaccuracy</t>
         </is>
       </c>
-      <c r="GK1" t="inlineStr">
+      <c r="GK1" s="1" t="inlineStr">
         <is>
           <t>unblockedlongmidrangeaccuracy</t>
         </is>
       </c>
-      <c r="GL1" t="inlineStr">
+      <c r="GL1" s="1" t="inlineStr">
         <is>
           <t>longmidrangepctassisted</t>
         </is>
       </c>
-      <c r="GM1" t="inlineStr">
+      <c r="GM1" s="1" t="inlineStr">
         <is>
           <t>corner3frequency</t>
         </is>
       </c>
-      <c r="GN1" t="inlineStr">
+      <c r="GN1" s="1" t="inlineStr">
         <is>
           <t>corner3accuracy</t>
         </is>
       </c>
-      <c r="GO1" t="inlineStr">
+      <c r="GO1" s="1" t="inlineStr">
         <is>
           <t>unblockedcorner3accuracy</t>
         </is>
       </c>
-      <c r="GP1" t="inlineStr">
+      <c r="GP1" s="1" t="inlineStr">
         <is>
           <t>corner3pctassisted</t>
         </is>
       </c>
-      <c r="GQ1" t="inlineStr">
+      <c r="GQ1" s="1" t="inlineStr">
         <is>
           <t>arc3frequency</t>
         </is>
       </c>
-      <c r="GR1" t="inlineStr">
+      <c r="GR1" s="1" t="inlineStr">
         <is>
           <t>arc3accuracy</t>
         </is>
       </c>
-      <c r="GS1" t="inlineStr">
+      <c r="GS1" s="1" t="inlineStr">
         <is>
           <t>unblockedarc3accuracy</t>
         </is>
       </c>
-      <c r="GT1" t="inlineStr">
+      <c r="GT1" s="1" t="inlineStr">
         <is>
           <t>arc3pctassisted</t>
         </is>
       </c>
-      <c r="GU1" t="inlineStr">
+      <c r="GU1" s="1" t="inlineStr">
         <is>
           <t>secondchanceatrimfrequency</t>
         </is>
       </c>
-      <c r="GV1" t="inlineStr">
+      <c r="GV1" s="1" t="inlineStr">
         <is>
           <t>secondchanceatrimaccuracy</t>
         </is>
       </c>
-      <c r="GW1" t="inlineStr">
+      <c r="GW1" s="1" t="inlineStr">
         <is>
           <t>secondchanceatrimpctassisted</t>
         </is>
       </c>
-      <c r="GX1" t="inlineStr">
+      <c r="GX1" s="1" t="inlineStr">
         <is>
           <t>secondchancecorner3frequency</t>
         </is>
       </c>
-      <c r="GY1" t="inlineStr">
+      <c r="GY1" s="1" t="inlineStr">
         <is>
           <t>secondchancecorner3accuracy</t>
         </is>
       </c>
-      <c r="GZ1" t="inlineStr">
+      <c r="GZ1" s="1" t="inlineStr">
         <is>
           <t>secondchancecorner3pctassisted</t>
         </is>
       </c>
-      <c r="HA1" t="inlineStr">
+      <c r="HA1" s="1" t="inlineStr">
         <is>
           <t>secondchancearc3frequency</t>
         </is>
       </c>
-      <c r="HB1" t="inlineStr">
+      <c r="HB1" s="1" t="inlineStr">
         <is>
           <t>secondchancearc3accuracy</t>
         </is>
       </c>
-      <c r="HC1" t="inlineStr">
+      <c r="HC1" s="1" t="inlineStr">
         <is>
           <t>secondchancearc3pctassisted</t>
         </is>
       </c>
-      <c r="HD1" t="inlineStr">
+      <c r="HD1" s="1" t="inlineStr">
         <is>
           <t>penaltyatrimfrequency</t>
         </is>
       </c>
-      <c r="HE1" t="inlineStr">
+      <c r="HE1" s="1" t="inlineStr">
         <is>
           <t>penaltyatrimaccuracy</t>
         </is>
       </c>
-      <c r="HF1" t="inlineStr">
+      <c r="HF1" s="1" t="inlineStr">
         <is>
           <t>penaltycorner3frequency</t>
         </is>
       </c>
-      <c r="HG1" t="inlineStr">
+      <c r="HG1" s="1" t="inlineStr">
         <is>
           <t>penaltycorner3accuracy</t>
         </is>
       </c>
-      <c r="HH1" t="inlineStr">
+      <c r="HH1" s="1" t="inlineStr">
         <is>
           <t>penaltyarc3frequency</t>
         </is>
       </c>
-      <c r="HI1" t="inlineStr">
+      <c r="HI1" s="1" t="inlineStr">
         <is>
           <t>penaltyarc3accuracy</t>
         </is>
       </c>
-      <c r="HJ1" t="inlineStr">
+      <c r="HJ1" s="1" t="inlineStr">
         <is>
           <t>atrimfg3afrequency</t>
         </is>
       </c>
-      <c r="HK1" t="inlineStr">
+      <c r="HK1" s="1" t="inlineStr">
         <is>
           <t>nonheavearc3accuracy</t>
         </is>
       </c>
-      <c r="HL1" t="inlineStr">
+      <c r="HL1" s="1" t="inlineStr">
         <is>
           <t>shotqualityavg</t>
         </is>
       </c>
-      <c r="HM1" t="inlineStr">
+      <c r="HM1" s="1" t="inlineStr">
         <is>
           <t>secondchanceshotqualityavg</t>
         </is>
       </c>
-      <c r="HN1" t="inlineStr">
+      <c r="HN1" s="1" t="inlineStr">
         <is>
           <t>penaltyshotqualityavg</t>
         </is>
       </c>
-      <c r="HO1" t="inlineStr">
+      <c r="HO1" s="1" t="inlineStr">
         <is>
           <t>shootingfoulsdrawnpct</t>
         </is>
       </c>
-      <c r="HP1" t="inlineStr">
+      <c r="HP1" s="1" t="inlineStr">
         <is>
           <t>twoptshootingfoulsdrawnpct</t>
         </is>
       </c>
-      <c r="HQ1" t="inlineStr">
+      <c r="HQ1" s="1" t="inlineStr">
         <is>
           <t>threeptshootingfoulsdrawnpct</t>
         </is>
       </c>
-      <c r="HR1" t="inlineStr">
+      <c r="HR1" s="1" t="inlineStr">
         <is>
           <t>secondchancepointspct</t>
         </is>
       </c>
-      <c r="HS1" t="inlineStr">
+      <c r="HS1" s="1" t="inlineStr">
         <is>
           <t>penaltypointspct</t>
         </is>
       </c>
-      <c r="HT1" t="inlineStr">
+      <c r="HT1" s="1" t="inlineStr">
         <is>
           <t>avg2ptshotdistance</t>
         </is>
       </c>
-      <c r="HU1" t="inlineStr">
+      <c r="HU1" s="1" t="inlineStr">
         <is>
           <t>avg3ptshotdistance</t>
         </is>
       </c>
-      <c r="HV1" t="inlineStr">
+      <c r="HV1" s="1" t="inlineStr">
         <is>
           <t>penaltyoffposspct</t>
         </is>
